--- a/data/trans_orig/IP2001-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2001-Edad-trans_orig.xlsx
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7232</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17187</t>
+          <t>18193</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6462</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17220</t>
+          <t>17060</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16194</t>
+          <t>16011</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30732</t>
+          <t>30529</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>234055</t>
+          <t>233049</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>244010</t>
+          <t>244300</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>233600</t>
+          <t>233760</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>244358</t>
+          <t>244140</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>471329</t>
+          <t>471532</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>485867</t>
+          <t>486050</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12449</t>
+          <t>12719</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24877</t>
+          <t>25194</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13118</t>
+          <t>13965</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25895</t>
+          <t>26420</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>27399</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45819</t>
+          <t>45645</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102137</t>
+          <t>101820</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114565</t>
+          <t>114295</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>114167</t>
+          <t>113642</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>126944</t>
+          <t>126097</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>221258</t>
+          <t>221432</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>239024</t>
+          <t>239678</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,74%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18804</t>
+          <t>19144</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33608</t>
+          <t>34519</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17144</t>
+          <t>16949</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31435</t>
+          <t>32493</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38836</t>
+          <t>38985</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60309</t>
+          <t>60121</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>159219</t>
+          <t>158308</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>174023</t>
+          <t>173683</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>170106</t>
+          <t>169048</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>184397</t>
+          <t>184592</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>334059</t>
+          <t>334247</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>355532</t>
+          <t>355383</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,11%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43146</t>
+          <t>43502</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66270</t>
+          <t>66367</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43736</t>
+          <t>43372</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67227</t>
+          <t>66992</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93664</t>
+          <t>92812</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124699</t>
+          <t>124278</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>575579</t>
+          <t>575482</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>598703</t>
+          <t>598347</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>610304</t>
+          <t>610539</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>633795</t>
+          <t>634159</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1194682</t>
+          <t>1195103</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1225717</t>
+          <t>1226569</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13588</t>
+          <t>13426</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27928</t>
+          <t>28122</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10855</t>
+          <t>11081</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25038</t>
+          <t>25824</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27647</t>
+          <t>28026</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48268</t>
+          <t>47812</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>207637</t>
+          <t>207443</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>221977</t>
+          <t>222139</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>243211</t>
+          <t>242425</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>257394</t>
+          <t>257168</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>455547</t>
+          <t>456003</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>476168</t>
+          <t>475789</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,44%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16521</t>
+          <t>16919</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31997</t>
+          <t>30868</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14251</t>
+          <t>14883</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29110</t>
+          <t>29044</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34710</t>
+          <t>35356</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56834</t>
+          <t>56457</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123946</t>
+          <t>125075</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>139422</t>
+          <t>139024</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>129461</t>
+          <t>129527</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>144320</t>
+          <t>143688</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>257680</t>
+          <t>258057</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>279804</t>
+          <t>279158</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,76%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11916</t>
+          <t>12377</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>25085</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20842</t>
+          <t>21421</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36993</t>
+          <t>35645</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36849</t>
+          <t>36377</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56403</t>
+          <t>57396</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143288</t>
+          <t>143757</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>156926</t>
+          <t>156465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>141129</t>
+          <t>142477</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>157280</t>
+          <t>156701</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>290560</t>
+          <t>289567</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>310114</t>
+          <t>310586</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,52%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51020</t>
+          <t>49264</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77399</t>
+          <t>74585</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53595</t>
+          <t>54990</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80425</t>
+          <t>81579</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109273</t>
+          <t>112165</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>147774</t>
+          <t>147484</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>581822</t>
+          <t>584636</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>608201</t>
+          <t>609957</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>620439</t>
+          <t>619285</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>647269</t>
+          <t>645874</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1212311</t>
+          <t>1212601</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1250812</t>
+          <t>1247920</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,75%</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77371</t>
+          <t>77063</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>165208</t>
+          <t>165276</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12122</t>
+          <t>12206</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25761</t>
+          <t>25776</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12150</t>
+          <t>11960</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26247</t>
+          <t>25610</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27307</t>
+          <t>27350</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46865</t>
+          <t>46862</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>184062</t>
+          <t>184047</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>197701</t>
+          <t>197617</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>231168</t>
+          <t>231805</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>245265</t>
+          <t>245455</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>420373</t>
+          <t>420376</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>439931</t>
+          <t>439888</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,15%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21949</t>
+          <t>22054</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38593</t>
+          <t>37844</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24669</t>
+          <t>23763</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41945</t>
+          <t>40133</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50820</t>
+          <t>50425</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73912</t>
+          <t>74400</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>149276</t>
+          <t>150025</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>165920</t>
+          <t>165815</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145983</t>
+          <t>147795</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163259</t>
+          <t>164165</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>301885</t>
+          <t>301397</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>324977</t>
+          <t>325372</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,58%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15176</t>
+          <t>15241</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30402</t>
+          <t>29987</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24612</t>
+          <t>24821</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30082</t>
+          <t>29733</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49595</t>
+          <t>49736</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>142899</t>
+          <t>143314</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158125</t>
+          <t>158060</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>149436</t>
+          <t>149227</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>162572</t>
+          <t>162531</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>297753</t>
+          <t>297612</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>317266</t>
+          <t>317615</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57365</t>
+          <t>57351</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83173</t>
+          <t>81317</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55615</t>
+          <t>55501</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82868</t>
+          <t>82084</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>120256</t>
+          <t>119580</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155821</t>
+          <t>153733</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>575679</t>
+          <t>577535</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>601487</t>
+          <t>601501</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>616737</t>
+          <t>617521</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>643990</t>
+          <t>644104</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1202636</t>
+          <t>1204724</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1238201</t>
+          <t>1238877</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5575</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42830</t>
+          <t>42930</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>90670</t>
+          <t>90277</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>2420</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10224</t>
+          <t>9846</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>5233</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16011</t>
+          <t>16159</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9963</t>
+          <t>10348</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22534</t>
+          <t>23691</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>147236</t>
+          <t>147614</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154603</t>
+          <t>155040</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>165552</t>
+          <t>165404</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>176184</t>
+          <t>176330</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>316490</t>
+          <t>315333</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>329061</t>
+          <t>328676</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17494</t>
+          <t>17009</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22514</t>
+          <t>23025</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17246</t>
+          <t>16814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34894</t>
+          <t>34558</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>155578</t>
+          <t>156063</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>166764</t>
+          <t>166858</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>189976</t>
+          <t>189465</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>204351</t>
+          <t>204133</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>350669</t>
+          <t>351005</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>368317</t>
+          <t>368749</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16329</t>
+          <t>16698</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13358</t>
+          <t>13848</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31853</t>
+          <t>31284</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22800</t>
+          <t>22466</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43590</t>
+          <t>44391</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>259129</t>
+          <t>258760</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>269724</t>
+          <t>269737</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>272148</t>
+          <t>272717</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>290643</t>
+          <t>290153</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>535869</t>
+          <t>535068</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>556659</t>
+          <t>556993</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20541</t>
+          <t>20251</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38987</t>
+          <t>38001</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33339</t>
+          <t>32717</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57334</t>
+          <t>57977</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58646</t>
+          <t>59127</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89442</t>
+          <t>89761</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>615409</t>
+          <t>616395</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>633855</t>
+          <t>634145</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>688650</t>
+          <t>688007</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>712645</t>
+          <t>713267</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1310937</t>
+          <t>1310618</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1341733</t>
+          <t>1341252</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2001-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2001-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,47 +836,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>85108</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>70767</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>85108</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>85108</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>85108</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>85108</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>70767</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>70767</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>70767</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>85108</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>85108</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>85108</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1071,67 +1071,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>11115</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16874</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,73%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>11306</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6942</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>18193</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6954</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>17577</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,5%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11115</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6680</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>17060</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16011</t>
+          <t>15732</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30529</t>
+          <t>30098</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>239705</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>233946</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>244332</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,27%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,41%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>359</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>239936</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>233049</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>244300</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>233665</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>244288</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,5%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,76%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,24%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>239705</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>233760</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>244140</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,57%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>471532</t>
+          <t>471963</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>486050</t>
+          <t>486329</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>250820</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>250820</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>250820</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>376</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>251242</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>251242</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>251242</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>250820</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>250820</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>250820</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19053</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12452</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>25907</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,6%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,89%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>17641</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12719</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>25194</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>12279</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>24811</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>13,89%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,84%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>19053</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>13965</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>26420</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>13,6%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27399</t>
+          <t>28726</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45645</t>
+          <t>46360</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>121009</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>114155</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>127610</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>86,4%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>81,5%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,11%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>109373</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>101820</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>114295</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>102203</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>114735</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>86,11%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>80,16%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>89,99%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>121009</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>113642</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>126097</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>86,4%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>221432</t>
+          <t>220717</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>239678</t>
+          <t>238351</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,24%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>140062</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>140062</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>140062</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127014</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127014</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127014</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>140062</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>140062</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>140062</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23919</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16916</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>32305</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11,87%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,39%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,03%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>25230</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>19144</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>34519</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>18500</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>33989</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>13,08%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,93%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>17,9%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>23919</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>16949</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>32493</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>11,87%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38985</t>
+          <t>39366</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60121</t>
+          <t>62686</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>177622</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>169236</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>184625</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>88,13%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>83,97%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>91,61%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>167597</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>158308</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>173683</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>158838</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>174327</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>86,92%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>82,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>90,07%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>177622</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>169048</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>184592</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>88,13%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>334247</t>
+          <t>331682</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>355383</t>
+          <t>355002</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,02%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>201541</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>201541</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>201541</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>284</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>192827</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>192827</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>192827</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>201541</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>201541</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>201541</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2100,67 +2100,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>54087</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>44124</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>65847</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,98%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,72%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>54177</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>43502</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>66367</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>43339</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>66323</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>8,44%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,78%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>54087</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>43372</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>66992</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,98%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92812</t>
+          <t>93753</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124278</t>
+          <t>124607</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>623444</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>611684</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>633407</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,02%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,28%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>93,49%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>877</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>587672</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>575482</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>598347</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>575526</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>598510</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>91,56%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,66%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,22%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>938</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>623444</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>610539</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>634159</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>92,02%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1195103</t>
+          <t>1194774</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1226569</t>
+          <t>1225628</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1019</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>677531</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>677531</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>677531</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>958</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>641849</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>641849</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>641849</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1019</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>677531</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>677531</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>677531</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2783,47 +2783,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>95923</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>98870</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>95923</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>95923</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>95923</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>95923</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>98870</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>98870</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>98870</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>95923</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>95923</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>95923</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17360</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11347</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>26331</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,47%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,82%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>19958</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>13426</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>28122</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>13512</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>28743</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>8,47%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,94%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>17360</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>11081</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>25824</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,47%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28026</t>
+          <t>28471</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47812</t>
+          <t>47391</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>250889</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>241918</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>256902</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,18%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,77%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>215607</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>207443</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>222139</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>206822</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>222053</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>91,53%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,06%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,3%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>250889</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>242425</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>257168</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,53%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>456003</t>
+          <t>456424</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>475789</t>
+          <t>475344</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268249</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268249</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268249</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>339</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>235565</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>235565</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>235565</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268249</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268249</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268249</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20775</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14121</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28633</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,1%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,91%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,06%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>23420</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16919</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>30868</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>17491</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>32001</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>15,02%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,85%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,79%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>20775</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>14883</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>29044</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>13,1%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35356</t>
+          <t>34546</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56457</t>
+          <t>55961</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>137796</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>129938</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>144450</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>86,9%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>81,94%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,09%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>132523</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>125075</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>139024</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>123942</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>138452</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>84,98%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>80,21%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>89,15%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>137796</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>129527</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>143688</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>86,9%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>258057</t>
+          <t>258553</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>279158</t>
+          <t>279968</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>89,02%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155943</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155943</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155943</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>27823</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20841</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>37057</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15,62%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,7%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20,8%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>18117</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12377</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>25085</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>12027</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>25421</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>10,73%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,33%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,86%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>27823</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>21421</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>35645</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>15,62%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36377</t>
+          <t>36455</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57396</t>
+          <t>56363</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>150299</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>141065</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>157281</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>84,38%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>79,2%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,3%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>150725</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>143757</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>156465</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>143421</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>156815</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>89,27%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>85,14%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,67%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>150299</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>142477</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>156701</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>84,38%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>289567</t>
+          <t>290600</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>310586</t>
+          <t>310508</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,49%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>178122</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>178122</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>178122</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>168842</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>168842</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>168842</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>178122</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>178122</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>178122</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>65958</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>53823</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>79914</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,41%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11,4%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>61495</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>49264</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>74585</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>48968</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>72618</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>9,33%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,47%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,31%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>65958</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>54990</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>81579</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>112165</t>
+          <t>110538</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>147484</t>
+          <t>146710</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>634906</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>620950</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>647041</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>90,59%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>88,6%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,32%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>861</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>597726</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>584636</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>609957</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>586603</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>610253</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>90,67%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>88,69%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,53%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>634906</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>619285</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>645874</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>90,59%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1212601</t>
+          <t>1213375</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1247920</t>
+          <t>1249547</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,87%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700864</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700864</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700864</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>949</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>659221</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>659221</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>659221</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>700864</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>700864</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>700864</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,107 +4617,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2874</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>558</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3151</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2819</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>558</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2798</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -4730,74 +4730,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>79656</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>77340</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>80214</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,42%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>87859</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>79656</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>77063</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>80214</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,07%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>262</t>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>165276</t>
+          <t>165255</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>80214</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>80214</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>80214</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>87859</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>87859</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>87859</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>80214</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>80214</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>80214</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18112</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11512</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25814</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,03%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>17989</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>12206</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>25776</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>12481</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>25926</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>8,57%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12,28%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>18112</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>11960</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>25610</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27350</t>
+          <t>27689</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46862</t>
+          <t>46183</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>239303</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>231601</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>245903</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,96%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,97%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,53%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>304</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>191834</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>184047</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>197617</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>183897</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>197342</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>91,43%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,72%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,18%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>239303</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>231805</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>245455</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,96%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>420376</t>
+          <t>421055</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>439888</t>
+          <t>439549</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,07%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>257415</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>257415</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>257415</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>331</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>209823</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>209823</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>209823</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>257415</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>257415</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>257415</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>31910</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24052</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>41474</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16,98%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12,8%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22,07%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>29773</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>22054</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>37844</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>22680</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>39514</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>15,85%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,74%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,14%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>31910</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>23763</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>40133</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>16,98%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50425</t>
+          <t>50077</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74400</t>
+          <t>73425</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>156018</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>146454</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>163876</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>83,02%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>77,93%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>87,2%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>158096</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>150025</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>165815</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>148355</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>165189</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>84,15%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>79,86%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>88,26%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>156018</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>147795</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>164165</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>83,02%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>301397</t>
+          <t>302372</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>325372</t>
+          <t>325720</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,67%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187928</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187928</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187928</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>187869</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>187869</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>187869</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187928</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187928</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187928</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17374</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11850</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25489</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,98%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,81%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14,64%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>21419</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15241</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>29987</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14478</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>29108</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>12,36%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,79%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>17,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>17374</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>11517</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>24821</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,98%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29733</t>
+          <t>28862</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49736</t>
+          <t>49454</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>148559</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>162198</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,02%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>85,36%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,19%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>151882</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>143314</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>158060</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>144193</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>158823</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>87,64%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>82,7%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,21%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>149227</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>162531</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>90,02%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>297612</t>
+          <t>297894</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>317615</t>
+          <t>318486</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,69%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>67954</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>55272</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>81936</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,9%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11,71%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>69182</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>57351</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>81317</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>56179</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>82855</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>10,5%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,34%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>67954</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>55501</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>82084</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>119580</t>
+          <t>119570</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>153733</t>
+          <t>157149</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>631651</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>617669</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>644333</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>90,29%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>88,29%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,1%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>885</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>589670</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>577535</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>601501</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>575997</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>602673</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>89,5%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,66%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>91,3%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>903</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>631651</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>617521</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>644104</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>90,29%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1204724</t>
+          <t>1201308</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1238877</t>
+          <t>1238887</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699605</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699605</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699605</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>989</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>658852</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>658852</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>658852</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>998</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>699605</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>699605</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>699605</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,107 +6564,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1637</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5475</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5103</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,31%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>11,45%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4930</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1637</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6057</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -6682,69 +6682,69 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46768</t>
+          <t>39676</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42930</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48405</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>43083</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>39460</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>44563</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>96,68%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>88,55%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>47929</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>174</t>
@@ -6752,27 +6752,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>94697</t>
+          <t>82759</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>90277</t>
+          <t>79309</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96334</t>
+          <t>84239</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>39676</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>39676</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>39676</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>48405</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>48405</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>48405</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>47929</t>
+          <t>44563</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47929</t>
+          <t>44563</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47929</t>
+          <t>44563</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>96334</t>
+          <t>84239</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>96334</t>
+          <t>84239</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>96334</t>
+          <t>84239</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8760</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4981</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15421</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,59%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,84%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5509</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2420</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9846</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>5085</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2208</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9061</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>1,54%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,25%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9616</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5233</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>16159</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>15126</t>
+          <t>13845</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10348</t>
+          <t>8981</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23691</t>
+          <t>21044</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -7020,74 +7020,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>147984</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>141323</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>151763</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,41%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,16%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,82%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>151951</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>147614</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>155040</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>96,5%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,75%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>138543</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>134567</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>141420</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>96,46%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>93,69%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>98,46%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>171947</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>165404</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>176330</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,7%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>91,1%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>97,12%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>504</t>
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>323898</t>
+          <t>286527</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>315333</t>
+          <t>279328</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>328676</t>
+          <t>291391</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156744</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156744</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156744</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>157460</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>157460</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>157460</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181563</t>
+          <t>143628</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181563</t>
+          <t>143628</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181563</t>
+          <t>143628</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>339024</t>
+          <t>300372</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>339024</t>
+          <t>300372</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>339024</t>
+          <t>300372</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13689</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7803</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21196</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,84%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,59%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10807</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6214</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17009</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,83%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13939</t>
+          <t>10985</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8357</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23025</t>
+          <t>17780</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>24746</t>
+          <t>24674</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16814</t>
+          <t>17039</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34558</t>
+          <t>34684</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>186437</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>178930</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>192323</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,16%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,41%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,1%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>162265</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>156063</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>166858</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>93,76%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,17%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,41%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>198551</t>
+          <t>163687</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>189465</t>
+          <t>156892</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>204133</t>
+          <t>168262</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>360817</t>
+          <t>350124</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>351005</t>
+          <t>340114</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>368749</t>
+          <t>357759</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20052</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12987</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>29691</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,89%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,2%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>10501</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5721</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>16698</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21203</t>
+          <t>10975</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13848</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31284</t>
+          <t>16976</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>31703</t>
+          <t>31028</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22466</t>
+          <t>22684</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44391</t>
+          <t>43197</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>271098</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>261459</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>278163</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,11%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,8%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,54%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>325</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>264957</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>258760</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>269737</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>96,19%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,92%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>282798</t>
+          <t>245578</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>272717</t>
+          <t>239577</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>290153</t>
+          <t>250187</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>547756</t>
+          <t>516675</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>535068</t>
+          <t>504506</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>556993</t>
+          <t>525019</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>291150</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>291150</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>291150</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>342</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>275458</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>275458</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>275458</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304001</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304001</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304001</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579459</t>
+          <t>547703</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579459</t>
+          <t>547703</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579459</t>
+          <t>547703</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>42502</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>31994</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>56115</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,65%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,16%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>28454</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>20251</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>38001</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>44758</t>
+          <t>28525</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32717</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57977</t>
+          <t>37760</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>73212</t>
+          <t>71027</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59127</t>
+          <t>57801</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89761</t>
+          <t>87760</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>645193</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>631580</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>655701</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,82%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,84%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,35%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>874</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>625942</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>616395</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>634145</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>95,65%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>94,19%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,91%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>701226</t>
+          <t>590891</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>688007</t>
+          <t>581656</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>713267</t>
+          <t>598893</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1327167</t>
+          <t>1236084</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1310618</t>
+          <t>1219351</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1341252</t>
+          <t>1249310</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>687695</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>687695</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>687695</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>918</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>654396</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>654396</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>654396</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>745984</t>
+          <t>619416</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>745984</t>
+          <t>619416</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>745984</t>
+          <t>619416</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1400379</t>
+          <t>1307111</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1400379</t>
+          <t>1307111</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1400379</t>
+          <t>1307111</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
